--- a/05_Figures/Proteome/F1_Overview/c_data/f1_overview_training.xlsx
+++ b/05_Figures/Proteome/F1_Overview/c_data/f1_overview_training.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="405">
   <si>
     <t>sheet</t>
   </si>
@@ -725,16 +725,16 @@
     <t>contrasts</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/03_Protein_Contrasts/training/c_data/protein_contrasts.xlsx</t>
-  </si>
-  <si>
-    <t>435fc143fa022d17ae3270ca9c35ffa8</t>
+    <t>03_Group_comparisons/Proteome/02_Protein_Contrasts/training/c_data/protein_contrasts.xlsx</t>
+  </si>
+  <si>
+    <t>0b58ca88d8192b6c9e2aed0c48ba327d</t>
   </si>
   <si>
     <t>set_tests</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/04_Set_Contrasts/training/c_data/set_tests.rds</t>
+    <t>03_Group_comparisons/Proteome/03_Set_Contrasts/training/c_data/set_tests.rds</t>
   </si>
   <si>
     <t>8b66fe3692e509d034ad57267d5a64d0</t>
@@ -749,22 +749,22 @@
     <t>bc1bf66e89df936e164c317354990470</t>
   </si>
   <si>
-    <t>00_Input/phenotype.csv</t>
+    <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
     <t>5a1989db406daa0b70189a9f0df52cf3</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/01_Clustering/c_data/clustering.xlsx</t>
-  </si>
-  <si>
-    <t>26ee0be84eef1dc9b7cd280844dda3e8</t>
+    <t>02_Groups/Proteome/c_data/clustering.xlsx</t>
+  </si>
+  <si>
+    <t>8e04a957cceabf91ead651b89d51dd35</t>
   </si>
   <si>
     <t>design</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/02_Design_Contrasts/training/c_data/design.rds</t>
+    <t>03_Group_comparisons/Proteome/01_Design_Contrasts/training/c_data/design.rds</t>
   </si>
   <si>
     <t>614bbdf4f0c26542c91ed8556721be1c</t>
@@ -875,12 +875,24 @@
     <t>1.2.1</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>foreach</t>
   </si>
   <si>
@@ -953,6 +965,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -965,6 +989,15 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -974,9 +1007,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -1013,6 +1043,9 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -1091,6 +1124,12 @@
     <t>1.3.0</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -1194,6 +1233,12 @@
   </si>
   <si>
     <t>xml2</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1766,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -1996,15 +2041,15 @@
         <v>296</v>
       </c>
       <c r="C25" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>297</v>
+      </c>
+      <c r="B26" t="s">
         <v>298</v>
-      </c>
-      <c r="B26" t="s">
-        <v>288</v>
       </c>
       <c r="C26" t="s">
         <v>253</v>
@@ -2018,15 +2063,15 @@
         <v>300</v>
       </c>
       <c r="C27" t="s">
-        <v>253</v>
+        <v>301</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C28" t="s">
         <v>253</v>
@@ -2073,7 +2118,7 @@
         <v>310</v>
       </c>
       <c r="C32" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2128,7 +2173,7 @@
         <v>320</v>
       </c>
       <c r="C37" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2136,7 +2181,7 @@
         <v>321</v>
       </c>
       <c r="B38" t="s">
-        <v>322</v>
+        <v>272</v>
       </c>
       <c r="C38" t="s">
         <v>253</v>
@@ -2144,10 +2189,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>322</v>
+      </c>
+      <c r="B39" t="s">
         <v>323</v>
-      </c>
-      <c r="B39" t="s">
-        <v>324</v>
       </c>
       <c r="C39" t="s">
         <v>253</v>
@@ -2155,10 +2200,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>324</v>
+      </c>
+      <c r="B40" t="s">
         <v>325</v>
-      </c>
-      <c r="B40" t="s">
-        <v>326</v>
       </c>
       <c r="C40" t="s">
         <v>253</v>
@@ -2166,10 +2211,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B41" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="C41" t="s">
         <v>253</v>
@@ -2177,32 +2222,32 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B42" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C42" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C43" t="s">
-        <v>253</v>
+        <v>301</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C44" t="s">
         <v>253</v>
@@ -2210,10 +2255,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C45" t="s">
         <v>253</v>
@@ -2221,10 +2266,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B46" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C46" t="s">
         <v>253</v>
@@ -2232,10 +2277,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B47" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C47" t="s">
         <v>253</v>
@@ -2243,10 +2288,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B48" t="s">
-        <v>342</v>
+        <v>300</v>
       </c>
       <c r="C48" t="s">
         <v>253</v>
@@ -2254,10 +2299,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B49" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C49" t="s">
         <v>253</v>
@@ -2265,10 +2310,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C50" t="s">
         <v>253</v>
@@ -2276,10 +2321,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B51" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C51" t="s">
         <v>253</v>
@@ -2287,10 +2332,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B52" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C52" t="s">
         <v>253</v>
@@ -2298,10 +2343,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B53" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C53" t="s">
         <v>253</v>
@@ -2309,21 +2354,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B54" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C54" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B55" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C55" t="s">
         <v>253</v>
@@ -2331,21 +2376,21 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C56" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B57" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C57" t="s">
         <v>253</v>
@@ -2353,10 +2398,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B58" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C58" t="s">
         <v>253</v>
@@ -2364,10 +2409,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B59" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C59" t="s">
         <v>253</v>
@@ -2375,10 +2420,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B60" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C60" t="s">
         <v>253</v>
@@ -2386,21 +2431,21 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B61" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C61" t="s">
-        <v>253</v>
+        <v>301</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B62" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C62" t="s">
         <v>253</v>
@@ -2408,10 +2453,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B63" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C63" t="s">
         <v>253</v>
@@ -2419,21 +2464,21 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B64" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C64" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B65" t="s">
-        <v>330</v>
+        <v>373</v>
       </c>
       <c r="C65" t="s">
         <v>253</v>
@@ -2441,10 +2486,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B66" t="s">
-        <v>282</v>
+        <v>375</v>
       </c>
       <c r="C66" t="s">
         <v>253</v>
@@ -2452,10 +2497,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
+        <v>376</v>
+      </c>
+      <c r="B67" t="s">
         <v>377</v>
-      </c>
-      <c r="B67" t="s">
-        <v>378</v>
       </c>
       <c r="C67" t="s">
         <v>253</v>
@@ -2463,10 +2508,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>378</v>
+      </c>
+      <c r="B68" t="s">
         <v>379</v>
-      </c>
-      <c r="B68" t="s">
-        <v>380</v>
       </c>
       <c r="C68" t="s">
         <v>253</v>
@@ -2474,10 +2519,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>380</v>
+      </c>
+      <c r="B69" t="s">
         <v>381</v>
-      </c>
-      <c r="B69" t="s">
-        <v>382</v>
       </c>
       <c r="C69" t="s">
         <v>253</v>
@@ -2485,10 +2530,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>382</v>
+      </c>
+      <c r="B70" t="s">
         <v>383</v>
-      </c>
-      <c r="B70" t="s">
-        <v>384</v>
       </c>
       <c r="C70" t="s">
         <v>253</v>
@@ -2496,21 +2541,21 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>384</v>
+      </c>
+      <c r="B71" t="s">
         <v>385</v>
       </c>
-      <c r="B71" t="s">
-        <v>386</v>
-      </c>
       <c r="C71" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>386</v>
+      </c>
+      <c r="B72" t="s">
         <v>387</v>
-      </c>
-      <c r="B72" t="s">
-        <v>388</v>
       </c>
       <c r="C72" t="s">
         <v>253</v>
@@ -2518,12 +2563,111 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
+        <v>388</v>
+      </c>
+      <c r="B73" t="s">
+        <v>341</v>
+      </c>
+      <c r="C73" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
         <v>389</v>
       </c>
-      <c r="B73" t="s">
-        <v>286</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="B74" t="s">
+        <v>282</v>
+      </c>
+      <c r="C74" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>390</v>
+      </c>
+      <c r="B75" t="s">
+        <v>391</v>
+      </c>
+      <c r="C75" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>392</v>
+      </c>
+      <c r="B76" t="s">
+        <v>393</v>
+      </c>
+      <c r="C76" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>394</v>
+      </c>
+      <c r="B77" t="s">
+        <v>395</v>
+      </c>
+      <c r="C77" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>396</v>
+      </c>
+      <c r="B78" t="s">
+        <v>397</v>
+      </c>
+      <c r="C78" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>398</v>
+      </c>
+      <c r="B79" t="s">
+        <v>399</v>
+      </c>
+      <c r="C79" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>400</v>
+      </c>
+      <c r="B80" t="s">
+        <v>401</v>
+      </c>
+      <c r="C80" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>402</v>
+      </c>
+      <c r="B81" t="s">
+        <v>290</v>
+      </c>
+      <c r="C81" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>403</v>
+      </c>
+      <c r="B82" t="s">
+        <v>404</v>
+      </c>
+      <c r="C82" t="s">
         <v>253</v>
       </c>
     </row>

--- a/05_Figures/Proteome/F1_Overview/c_data/f1_overview_training.xlsx
+++ b/05_Figures/Proteome/F1_Overview/c_data/f1_overview_training.xlsx
@@ -728,7 +728,7 @@
     <t>03_Group_comparisons/Proteome/02_Protein_Contrasts/training/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>0b58ca88d8192b6c9e2aed0c48ba327d</t>
+    <t>2104a47ea9db38c511b850d3c1a4701e</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -758,7 +758,7 @@
     <t>02_Groups/Proteome/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>8e04a957cceabf91ead651b89d51dd35</t>
+    <t>65506da788b47182e1478149f673bdfd</t>
   </si>
   <si>
     <t>design</t>
